--- a/Dashboards/Data final/salarios_series.xlsx
+++ b/Dashboards/Data final/salarios_series.xlsx
@@ -407,7 +407,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>170</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>200</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>218</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="C10">
-        <v>240</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="C12">
-        <v>264</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>292</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C16">
-        <v>318</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>340</v>
+        <v>354</v>
       </c>
     </row>
     <row r="19">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="C20">
-        <v>354</v>
+        <v>366</v>
       </c>
     </row>
     <row r="21">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="23">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="C24">
-        <v>375</v>
+        <v>386</v>
       </c>
     </row>
     <row r="25">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="C26">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="27">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="C28">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="29">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C32">
-        <v>400</v>
+        <v>425</v>
       </c>
     </row>
     <row r="33">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="C34">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row r="35">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C36">
-        <v>425</v>
+        <v>460</v>
       </c>
     </row>
     <row r="37">
